--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -425,6 +425,10 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -440,17 +444,37 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>New High %</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>New Low</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>New Low %</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Advancing</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Advancing %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Declining</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Declining %</t>
         </is>
       </c>
     </row>
@@ -467,17 +491,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>50.6%</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>49.4%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>2368</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>42.3%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>3015</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>53.9%</t>
         </is>
       </c>
     </row>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -525,6 +525,53 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>50.6%</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>49.4%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>42.3%</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3015</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>53.9%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -533,42 +533,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>175</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>46.5%</t>
         </is>
       </c>
     </row>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -572,6 +572,53 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2729</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>48.7%</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2635</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -619,6 +619,53 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>65.9%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>34.1%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>3684</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>65.7%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -666,6 +666,53 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>67.2%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>32.8%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2825</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>50.4%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2566</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -713,6 +713,53 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>66.2%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>33.8%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2581</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>46.1%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2802</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -760,6 +760,53 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>83.9%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>3086</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>55.0%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>41.8%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -807,6 +807,53 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>41.2%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>58.8%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>23.2%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>34.1%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -854,6 +854,53 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>33.9%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>66.1%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>26.2%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1487</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>26.4%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -901,6 +901,53 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>63.4%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>36.6%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>35.6%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -948,6 +948,53 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>55.0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1839</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>32.7%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
